--- a/templates/time_sheet_template.xlsx
+++ b/templates/time_sheet_template.xlsx
@@ -55,7 +55,7 @@
     <t>Klient*in:</t>
   </si>
   <si>
-    <t>Klient-Nr.:</t>
+    <t>Auftrag-Nr.:</t>
   </si>
   <si>
     <t>Uhrzeit</t>
